--- a/temp/pages/all-profiles.xlsx
+++ b/temp/pages/all-profiles.xlsx
@@ -1808,7 +1808,7 @@
     <t>OID:2.16.840.1.113883.2.22.40.14.42.2</t>
   </si>
   <si>
-    <t>2026-10-16T16:15:28-03:00</t>
+    <t>2026-10-22T10:20:43-03:00</t>
   </si>
   <si>
     <t>Perfil asociado al listado de documentos referenciados para HSI en un modelo MHD</t>
